--- a/storage/programas/2/evidencias/elemento_6_y_7/actividad_4_2/template_evidencia_actividad_9_revisi_n_aleatoria_del_lista_de_chequeo_en_sistema.xlsx
+++ b/storage/programas/2/evidencias/elemento_6_y_7/actividad_4_2/template_evidencia_actividad_9_revisi_n_aleatoria_del_lista_de_chequeo_en_sistema.xlsx
@@ -4,15 +4,191 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Check Camión DI GR" state="visible" r:id="rId3"/>
+    <sheet sheetId="1" name="Check List Camión Granel" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="57">
+  <si>
+    <t>CHECK LIST CAMIONES TRANSPORTE GRANEL</t>
+  </si>
+  <si>
+    <t>Gerencia Operaciones</t>
+  </si>
+  <si>
+    <t>Fecha actualización: 04-03-2026</t>
+  </si>
+  <si>
+    <t>Dependencia</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Hora</t>
+  </si>
+  <si>
+    <t>Chofer</t>
+  </si>
+  <si>
+    <t>Contratista</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>AUTOCONTROL PRIMARIO INICIO JORNADA (Responsable: Tripulación)</t>
+  </si>
+  <si>
+    <t>a) DOCUMENTACIÓN</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>01. ¿Revisión técnica vigente?</t>
+  </si>
+  <si>
+    <t>02. ¿Licencia de conducir?</t>
+  </si>
+  <si>
+    <t>03. ¿Permiso de circulación vigente?</t>
+  </si>
+  <si>
+    <t>04. ¿Seguro obligatorio?</t>
+  </si>
+  <si>
+    <t>05. ¿Registro SEC?</t>
+  </si>
+  <si>
+    <t>06. ¿Nómina de personal autorizado actualizada?</t>
+  </si>
+  <si>
+    <t>07. ¿Hoja de datos de seguridad?</t>
+  </si>
+  <si>
+    <t>b) ELEMENTOS DE SEGURIDAD</t>
+  </si>
+  <si>
+    <t>08. ¿Extintor vigente y operativo?</t>
+  </si>
+  <si>
+    <t>09. ¿Botiquín completo?</t>
+  </si>
+  <si>
+    <t>10. ¿Triángulos reflectantes?</t>
+  </si>
+  <si>
+    <t>11. ¿Chaleco reflectante?</t>
+  </si>
+  <si>
+    <t>12. ¿Kit antiderrame?</t>
+  </si>
+  <si>
+    <t>13. ¿Cuñas para ruedas?</t>
+  </si>
+  <si>
+    <t>c) CARROCERÍA</t>
+  </si>
+  <si>
+    <t>14. ¿Piso de la carrocería en buen estado?</t>
+  </si>
+  <si>
+    <t>15. ¿Escalones/pisaderas completos y en buen estado?</t>
+  </si>
+  <si>
+    <t>16. ¿Planchas metálicas móviles en buen estado?</t>
+  </si>
+  <si>
+    <t>17. ¿Carrocería, bisagras y estructura en buen estado?</t>
+  </si>
+  <si>
+    <t>18. ¿Puertas en buen estado Art. 112 DS 108?</t>
+  </si>
+  <si>
+    <t>19. ¿Tensores superiores en buen estado?</t>
+  </si>
+  <si>
+    <t>20. ¿Neumáticos en buen estado?</t>
+  </si>
+  <si>
+    <t>d) EQUIPOS DE PROTECCIÓN</t>
+  </si>
+  <si>
+    <t>21. ¿Casco de seguridad?</t>
+  </si>
+  <si>
+    <t>22. ¿Guantes de seguridad?</t>
+  </si>
+  <si>
+    <t>23. ¿Zapatos de seguridad?</t>
+  </si>
+  <si>
+    <t>24. ¿Lentes de seguridad?</t>
+  </si>
+  <si>
+    <t>25. ¿Protección auditiva?</t>
+  </si>
+  <si>
+    <t>e) MARCAS Y ETIQUETAS</t>
+  </si>
+  <si>
+    <t>26. Rombos "GAS LICUADO INFLAMABLE - 2" (1 por cada lado)</t>
+  </si>
+  <si>
+    <t>27. Número UN "1075" (1 por cada lado)</t>
+  </si>
+  <si>
+    <t>28. Leyenda parabrisas "GAS LICUADO INFLAMABLE" Art. 74 DS 108</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>CONTROL AUTORIZACIÓN SALIDA (Responsable: Tripulación)</t>
+  </si>
+  <si>
+    <t>29. ¿Las puertas están aseguradas con pestillos cerrados y con candados?</t>
+  </si>
+  <si>
+    <t>30. ¿Las puertas traseras son utilizadas como elementos de contención?</t>
+  </si>
+  <si>
+    <t>31. ¿Se observan cilindros acostados, derrumbados o sueltos?</t>
+  </si>
+  <si>
+    <t>32. ¿Se asegura la carga mediante eslingas en buen estado?</t>
+  </si>
+  <si>
+    <t>33. ¿Las eslingas están correctamente afianzadas a la carrocería?</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>Firma Conductor</t>
+  </si>
+  <si>
+    <t>Firma Supervisor / Despachador</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -20,16 +196,73 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="003594"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="374151"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003594"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="E8F0FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="475569"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -37,12 +270,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,12 +643,1362 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:T55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="16384" width="2.54296875" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="20" width="8" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="G5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S39" s="6"/>
+      <c r="T39" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q45" s="6"/>
+      <c r="R45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S45" s="6"/>
+      <c r="T45" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="7"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="7"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7"/>
+      <c r="S49" s="7"/>
+      <c r="T49" s="7"/>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7"/>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="7"/>
+      <c r="T50" s="7"/>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="T52" s="5"/>
+    </row>
+    <row r="53" ht="60" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="133">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:T2"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:T9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="A16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="A21:O21"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="A33:O33"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="A34:O34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="A35:O35"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="A42:O42"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:T44"/>
+    <mergeCell ref="A45:O45"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="A46:O46"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="A47:O47"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="A48:O48"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="A49:O49"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="A50:O50"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="A52:T52"/>
+    <mergeCell ref="A53:T53"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="K55:T55"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
